--- a/#Valorant_anonymized.xlsx
+++ b/#Valorant_anonymized.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -5890,7 +5890,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10856,7 +10856,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11400,7 +11400,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12094,7 +12094,7 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -13520,7 +13520,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -16307,7 +16307,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17012,7 +17012,7 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17735,7 +17735,7 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19173,7 +19173,7 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19480,7 +19480,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20204,7 +20204,7 @@
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20930,7 +20930,7 @@
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20980,7 +20980,7 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -21628,7 +21628,7 @@
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22204,7 +22204,7 @@
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23214,7 @@
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -23953,7 +23953,7 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24000,7 +24000,7 @@
       </c>
       <c r="J696" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -24690,7 +24690,7 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25249,7 +25249,7 @@
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -25776,7 +25776,7 @@
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26445,7 +26445,7 @@
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -27562,7 +27562,7 @@
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -28915,7 +28915,7 @@
       </c>
       <c r="J842" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29585,7 +29585,7 @@
       </c>
       <c r="J862" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30296,7 +30296,7 @@
       </c>
       <c r="J883" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -30949,7 +30949,7 @@
       </c>
       <c r="J903" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -31633,7 +31633,7 @@
       </c>
       <c r="J924" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32315,7 +32315,7 @@
       </c>
       <c r="J945" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32455,7 +32455,7 @@
       </c>
       <c r="J949" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -32493,7 +32493,7 @@
       </c>
       <c r="J950" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -33034,7 +33034,7 @@
       </c>
       <c r="J966" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
